--- a/Cards.xlsx
+++ b/Cards.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Egyetem\VI. félév\kartya-szamlalo-alkalmazas\images\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Egyetem\VI. félév\Képfeldolgozás\kartya-szamlalo-alkalmazas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFE8307E-0E48-4A4B-B50B-DEDF8A5CFC15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFFE3DB1-8DEC-4164-8D37-6C59476116DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14092" xr2:uid="{0D6503BF-8C2F-49CD-A8C5-6BF1049C6181}"/>
+    <workbookView xWindow="3975" yWindow="3975" windowWidth="21600" windowHeight="11385" xr2:uid="{0D6503BF-8C2F-49CD-A8C5-6BF1049C6181}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -436,9 +436,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E036726E-A29E-4C2B-88D0-BE406ECFED10}">
   <dimension ref="A1:C104"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>1</v>
       </c>
@@ -449,7 +449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2</v>
       </c>
@@ -460,7 +460,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>3</v>
       </c>
@@ -471,7 +471,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>4</v>
       </c>
@@ -482,7 +482,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>5</v>
       </c>
@@ -493,7 +493,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>6</v>
       </c>
@@ -504,7 +504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>7</v>
       </c>
@@ -515,7 +515,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>8</v>
       </c>
@@ -526,7 +526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9</v>
       </c>
@@ -537,7 +537,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>10</v>
       </c>
@@ -548,7 +548,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>11</v>
       </c>
@@ -559,7 +559,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>12</v>
       </c>
@@ -570,7 +570,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>13</v>
       </c>
@@ -581,7 +581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>14</v>
       </c>
@@ -592,7 +592,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>15</v>
       </c>
@@ -603,7 +603,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>16</v>
       </c>
@@ -614,7 +614,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>17</v>
       </c>
@@ -625,7 +625,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>18</v>
       </c>
@@ -636,7 +636,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>19</v>
       </c>
@@ -647,7 +647,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>20</v>
       </c>
@@ -658,7 +658,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>21</v>
       </c>
@@ -669,7 +669,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>22</v>
       </c>
@@ -680,7 +680,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>23</v>
       </c>
@@ -691,7 +691,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>24</v>
       </c>
@@ -702,7 +702,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>25</v>
       </c>
@@ -713,7 +713,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26</v>
       </c>
@@ -724,7 +724,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>27</v>
       </c>
@@ -735,7 +735,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>28</v>
       </c>
@@ -746,7 +746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>29</v>
       </c>
@@ -757,7 +757,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>30</v>
       </c>
@@ -768,7 +768,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>31</v>
       </c>
@@ -779,7 +779,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>32</v>
       </c>
@@ -790,7 +790,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>33</v>
       </c>
@@ -801,7 +801,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>34</v>
       </c>
@@ -812,7 +812,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>35</v>
       </c>
@@ -823,7 +823,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>36</v>
       </c>
@@ -834,7 +834,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>37</v>
       </c>
@@ -845,7 +845,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>38</v>
       </c>
@@ -856,7 +856,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>39</v>
       </c>
@@ -867,7 +867,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>40</v>
       </c>
@@ -878,7 +878,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>41</v>
       </c>
@@ -889,7 +889,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>42</v>
       </c>
@@ -900,7 +900,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>43</v>
       </c>
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>44</v>
       </c>
@@ -922,7 +922,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>45</v>
       </c>
@@ -933,7 +933,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>46</v>
       </c>
@@ -944,7 +944,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>47</v>
       </c>
@@ -955,7 +955,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>48</v>
       </c>
@@ -966,7 +966,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>49</v>
       </c>
@@ -977,7 +977,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>50</v>
       </c>
@@ -988,7 +988,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>51</v>
       </c>
@@ -999,7 +999,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>52</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>53</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>54</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>55</v>
       </c>
@@ -1043,7 +1043,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>56</v>
       </c>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>57</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>58</v>
       </c>
@@ -1076,7 +1076,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>59</v>
       </c>
@@ -1087,7 +1087,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>60</v>
       </c>
@@ -1098,7 +1098,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>61</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>62</v>
       </c>
@@ -1120,7 +1120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>63</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>64</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>65</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>66</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>67</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>68</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>69</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>70</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>71</v>
       </c>
@@ -1219,7 +1219,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>72</v>
       </c>
@@ -1230,7 +1230,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>73</v>
       </c>
@@ -1241,7 +1241,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>74</v>
       </c>
@@ -1252,7 +1252,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>75</v>
       </c>
@@ -1263,7 +1263,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>76</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>77</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>78</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>79</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>80</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>81</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>82</v>
       </c>
@@ -1340,7 +1340,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>83</v>
       </c>
@@ -1351,7 +1351,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>84</v>
       </c>
@@ -1362,7 +1362,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>85</v>
       </c>
@@ -1373,7 +1373,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>86</v>
       </c>
@@ -1384,7 +1384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>87</v>
       </c>
@@ -1395,7 +1395,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>88</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>89</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>90</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>91</v>
       </c>
@@ -1439,7 +1439,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>92</v>
       </c>
@@ -1450,7 +1450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>93</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>94</v>
       </c>
@@ -1472,7 +1472,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>95</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>96</v>
       </c>
@@ -1494,7 +1494,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>97</v>
       </c>
@@ -1505,7 +1505,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>98</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>99</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>100</v>
       </c>
@@ -1538,7 +1538,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>101</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>102</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>103</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>104</v>
       </c>
